--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
   <si>
     <t>Filename</t>
   </si>
@@ -811,661 +811,676 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9918,0.0006,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9974,0.0002,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0478,0.0001,0.0000,0.9882</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9925,0.0008,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.0139,0.0003,0.0011,0.9917</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.9961,0.0009</t>
+  </si>
+  <si>
+    <t>0.1034,0.0001,0.9613,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0008,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9590,0.0007,0.0125,0.0023</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.9960,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.0403,0.9733,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9791,0.0002,0.0140,0.0002</t>
+  </si>
+  <si>
+    <t>0.1664,0.0013,0.8599,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0006,0.9948,0.0002</t>
+  </si>
+  <si>
+    <t>0.6854,0.0002,0.3958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9994,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.9970,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9930,0.0040,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.9708,0.0602,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.4276,0.6440,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.9944,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0456,0.9677,0.0022</t>
+  </si>
+  <si>
+    <t>0.0016,0.0013,0.9939,0.0011</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.9181,0.0000,0.1537,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.0353,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.0031,0.9539,0.0573,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9529,0.0023,0.9251</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0033,0.9988,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0448,0.9932,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0008,0.9973,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0069,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0046,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0225,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0106,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9767,0.4569,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0024,0.9967,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9852,0.0007,0.0088,0.0001</t>
+  </si>
+  <si>
+    <t>0.8211,0.0037,0.1584,0.0014</t>
+  </si>
+  <si>
+    <t>0.0009,0.0019,0.9977,0.0027</t>
+  </si>
+  <si>
+    <t>0.0000,0.9946,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.8489,0.8858,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9980,0.0474,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0092,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0001,0.1072,0.9580</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0011,0.9997</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9977,0.2241,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9931,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0853,0.9620,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9475,0.9856,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9809,0.9885,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0084,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0049,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0010,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0104,0.0103,0.9908,0.0001</t>
+  </si>
+  <si>
+    <t>0.9890,0.0017,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.9948,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.4142,0.6180,0.0073,0.0006</t>
+  </si>
+  <si>
+    <t>0.8453,0.0255,0.0535,0.0020</t>
+  </si>
+  <si>
+    <t>0.9398,0.0026,0.0354,0.0003</t>
+  </si>
+  <si>
+    <t>0.0037,0.1582,0.2055,0.1066</t>
+  </si>
+  <si>
+    <t>0.0201,0.0046,0.9718,0.0013</t>
+  </si>
+  <si>
+    <t>0.0062,0.3823,0.0124,0.7969</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9936,0.9730,0.0000</t>
+  </si>
+  <si>
+    <t>0.9626,0.0457,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.7773,0.2135,0.0157,0.0042</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0096,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9146,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0187,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0937,0.0006,0.9230,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3392,0.0009,0.5360,0.0033</t>
+  </si>
+  <si>
+    <t>0.0108,0.0000,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.9051,0.0025,0.0627,0.0015</t>
+  </si>
+  <si>
+    <t>0.0300,0.0010,0.0000,0.9902</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9932,0.9667,0.0000</t>
+  </si>
+  <si>
+    <t>0.4648,0.5672,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1726,0.8490,0.0041,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0920,0.0000,0.0013,0.9482</t>
+  </si>
+  <si>
+    <t>0.0013,0.0105,0.9974,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.4106,0.5055,0.0115,0.0020</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9577,0.0230,0.0057,0.0017</t>
+  </si>
+  <si>
+    <t>0.3311,0.6537,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9516,0.0033,0.0224,0.0007</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9572,0.0637,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.3659,0.6683,0.0148,0.0003</t>
+  </si>
+  <si>
+    <t>0.0493,0.9636,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9283,0.0551,0.0074,0.0068</t>
+  </si>
+  <si>
+    <t>0.9935,0.0094,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9857,0.0092,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0086,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9568,0.0303,0.0121,0.0070</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0018,0.9980,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0134,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0253,0.0112,0.8946,0.0023</t>
+  </si>
+  <si>
+    <t>0.0853,0.0006,0.9529,0.0001</t>
+  </si>
+  <si>
+    <t>0.0050,0.0013,0.9915,0.0008</t>
+  </si>
+  <si>
+    <t>0.0274,0.1459,0.7140,0.0004</t>
+  </si>
+  <si>
+    <t>0.0102,0.0096,0.9763,0.0005</t>
+  </si>
+  <si>
+    <t>0.1128,0.0159,0.6912,0.0040</t>
+  </si>
+  <si>
+    <t>0.9483,0.0017,0.0143,0.0025</t>
+  </si>
+  <si>
+    <t>0.0470,0.0040,0.9514,0.0013</t>
+  </si>
+  <si>
+    <t>0.0067,0.9939,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0064,0.9954,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9455,0.1043,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.1458,0.9055,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0107,0.9926,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8734,0.0033,0.0843,0.0015</t>
+  </si>
+  <si>
+    <t>0.9461,0.0020,0.0304,0.0008</t>
+  </si>
+  <si>
+    <t>0.9663,0.0036,0.0022,0.0055</t>
+  </si>
+  <si>
+    <t>0.8414,0.0155,0.0829,0.0019</t>
+  </si>
+  <si>
+    <t>0.4500,0.0012,0.4274,0.0053</t>
+  </si>
+  <si>
+    <t>0.0017,0.0005,0.9958,0.0028</t>
+  </si>
+  <si>
+    <t>0.0007,0.0062,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0136,0.9933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0085,0.0010,0.9895,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9207,0.7066,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0022,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0114,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0421,0.1632,0.5370,0.0009</t>
+  </si>
+  <si>
+    <t>0.9734,0.0008,0.0101,0.0004</t>
+  </si>
+  <si>
+    <t>0.0121,0.0003,0.9892,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.6433,0.9723,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0040,0.9960,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9965,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.0024,0.9939,0.0019</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.4585,0.0003,0.6402,0.0009</t>
+  </si>
+  <si>
+    <t>0.9933,0.0004,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0028,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9995,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9026,0.0021,0.0629,0.0007</t>
-  </si>
-  <si>
-    <t>0.0036,0.0006,0.9950,0.0004</t>
-  </si>
-  <si>
-    <t>0.3272,0.0019,0.7318,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0024,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.9576,0.0006,0.0273,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0262,0.9746,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.0030,0.9964,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9560,0.0001,0.0480,0.0001</t>
-  </si>
-  <si>
-    <t>0.0107,0.0016,0.9862,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0005,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.3066,0.0001,0.8022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.0000,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9985,0.0036</t>
-  </si>
-  <si>
-    <t>0.0255,0.9713,0.0011,0.0055</t>
-  </si>
-  <si>
-    <t>0.9850,0.0013,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9714,0.0016,0.0097,0.0005</t>
-  </si>
-  <si>
-    <t>0.5068,0.5337,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.0068,0.9615,0.1352,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.1662,0.9864,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9986,0.0004</t>
-  </si>
-  <si>
-    <t>0.0044,0.0010,0.9918,0.0003</t>
-  </si>
-  <si>
-    <t>0.1586,0.0001,0.8945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0041,0.0374,0.9914,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.9892,0.0085,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9357,0.0034,0.8952</t>
-  </si>
-  <si>
-    <t>0.0010,0.9966,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0072,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0213,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0313,0.0002,0.9725,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0038,0.9970,0.0006</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9876,0.0090,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9386,0.0686,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9615,0.8176,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0139,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9985,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9984,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9786,0.0006,0.0168,0.0001</t>
-  </si>
-  <si>
-    <t>0.4328,0.0050,0.4650,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.0030,0.9952,0.0040</t>
-  </si>
-  <si>
-    <t>0.0000,0.9878,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9109,0.8308,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9976,0.1027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.2918,0.9723</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0008,0.9990</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0027,0.9993</t>
+    <t>0.0003,0.0002,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0073,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0035,0.9949,0.0014</t>
+  </si>
+  <si>
+    <t>0.0067,0.0021,0.9921,0.0001</t>
+  </si>
+  <si>
+    <t>0.0297,0.0005,0.9697,0.0025</t>
+  </si>
+  <si>
+    <t>0.8621,0.0025,0.1014,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0013,0.9842,0.0075</t>
+  </si>
+  <si>
+    <t>0.4208,0.0000,0.0020,0.6125</t>
+  </si>
+  <si>
+    <t>0.1589,0.0369,0.0000,0.7079</t>
+  </si>
+  <si>
+    <t>0.0220,0.0001,0.0002,0.9934</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9986,0.0197,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9921,0.9872,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.5605,0.9865,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8183,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9726,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9939,0.1057,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0034,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0003,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0011,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0005,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0645,0.9606,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.2209,0.8641,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.6295,0.0394,0.1174,0.0012</t>
-  </si>
-  <si>
-    <t>0.6429,0.0324,0.1002,0.0014</t>
-  </si>
-  <si>
-    <t>0.0937,0.0034,0.8063,0.0267</t>
-  </si>
-  <si>
-    <t>0.0200,0.0090,0.9463,0.0023</t>
-  </si>
-  <si>
-    <t>0.0032,0.3450,0.0030,0.9381</t>
-  </si>
-  <si>
-    <t>0.0003,0.9983,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9603,0.8842,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.8186,0.2109,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.7712,0.2544,0.0046,0.0009</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0018,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.7689,0.9846,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.5778,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0297,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0076,0.9938,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9885,0.0027,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.0039,0.0000,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.9806,0.0002,0.0110,0.0002</t>
-  </si>
-  <si>
-    <t>0.1258,0.0015,0.0000,0.9546</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9950,0.9821,0.0000</t>
-  </si>
-  <si>
-    <t>0.0674,0.9234,0.0032,0.0016</t>
-  </si>
-  <si>
-    <t>0.0127,0.9799,0.0102,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8462,0.0001,0.0012,0.1164</t>
-  </si>
-  <si>
-    <t>0.0002,0.0040,0.9995,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0000,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.8748,0.0666,0.0133,0.0019</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2117,0.4611,0.0333,0.0040</t>
-  </si>
-  <si>
-    <t>0.9789,0.0064,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9877,0.0183,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7973,0.2156,0.0073,0.0003</t>
-  </si>
-  <si>
-    <t>0.7628,0.3327,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.1277,0.7238,0.2332,0.0007</t>
-  </si>
-  <si>
-    <t>0.9974,0.0022,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9846,0.0085,0.0029,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0131,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.9898,0.0030,0.0032,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.0002,0.9972,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0552,0.0005,0.9537,0.0008</t>
-  </si>
-  <si>
-    <t>0.0122,0.0001,0.9938,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0013,0.9961,0.0012</t>
-  </si>
-  <si>
-    <t>0.2213,0.1240,0.3327,0.0003</t>
-  </si>
-  <si>
-    <t>0.0132,0.0045,0.9762,0.0003</t>
-  </si>
-  <si>
-    <t>0.1989,0.0038,0.7803,0.0011</t>
-  </si>
-  <si>
-    <t>0.9915,0.0013,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.1590,0.0077,0.8454,0.0006</t>
-  </si>
-  <si>
-    <t>0.0287,0.9830,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.9976,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9656,0.0645,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.9949,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0350,0.9796,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9727,0.0056,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.9769,0.0001,0.0212,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9322,0.0101,0.0086,0.0032</t>
-  </si>
-  <si>
-    <t>0.1854,0.0029,0.7386,0.0024</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.9961,0.0088</t>
-  </si>
-  <si>
-    <t>0.0007,0.0025,0.9970,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0797,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0071,0.0002,0.9932,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.3086,0.9392,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0285,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0241,0.5070,0.3861,0.0039</t>
-  </si>
-  <si>
-    <t>0.0831,0.0006,0.8949,0.0027</t>
-  </si>
-  <si>
-    <t>0.0042,0.0001,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0020,0.9984,0.0005</t>
-  </si>
-  <si>
-    <t>0.0013,0.0384,0.9925,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0002,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0011,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0008,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0014,0.9965,0.0005</t>
-  </si>
-  <si>
-    <t>0.9934,0.0001,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9641,0.0001,0.0246,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0001,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0747,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0103,0.9883,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0004,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.3707,0.0006,0.6101,0.0036</t>
-  </si>
-  <si>
-    <t>0.5068,0.0012,0.4585,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0027,0.9954,0.0009</t>
-  </si>
-  <si>
-    <t>0.9766,0.0001,0.0005,0.0160</t>
-  </si>
-  <si>
-    <t>0.0081,0.1155,0.0001,0.9830</t>
-  </si>
-  <si>
-    <t>0.0028,0.0001,0.0001,0.9991</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0001,0.0013</t>
+    <t>0.9989,0.0004,0.0001,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1851,7 +1866,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1865,7 +1880,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1879,7 +1894,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1893,7 +1908,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1907,7 +1922,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1921,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1935,7 +1950,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1949,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1977,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2005,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2212,7 +2227,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
         <v>288</v>
@@ -2408,7 +2423,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
         <v>302</v>
@@ -2702,7 +2717,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
         <v>323</v>
@@ -3010,7 +3025,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>345</v>
@@ -3069,7 +3084,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3083,7 +3098,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3097,7 +3112,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3111,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3139,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3153,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3181,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3209,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3237,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3251,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3265,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3279,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3405,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3419,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3433,7 +3448,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3447,7 +3462,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3461,7 +3476,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3472,10 +3487,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3489,7 +3504,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3503,7 +3518,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3517,7 +3532,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3531,7 +3546,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3545,7 +3560,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3559,7 +3574,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3573,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3587,7 +3602,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3601,7 +3616,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3615,7 +3630,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>296</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3629,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3643,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3685,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3699,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3713,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>378</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3724,10 +3739,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3741,7 +3756,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3755,7 +3770,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3769,7 +3784,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3783,7 +3798,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3794,10 +3809,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3811,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3825,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3839,7 +3854,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3853,7 +3868,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3867,7 +3882,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3881,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3895,7 +3910,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3909,7 +3924,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3923,7 +3938,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3937,7 +3952,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>392</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3951,7 +3966,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3965,7 +3980,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3976,10 +3991,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3993,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4007,7 +4022,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4021,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4035,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4046,10 +4061,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4063,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4077,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4088,10 +4103,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4105,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4119,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4133,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4147,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>406</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4161,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4175,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>269</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4189,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4203,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4217,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4231,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4245,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4256,10 +4271,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4270,10 +4285,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4284,10 +4299,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4301,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4315,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4329,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>407</v>
+        <v>272</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4343,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4357,7 +4372,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4371,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4385,7 +4400,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4399,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4413,7 +4428,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4427,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4441,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4455,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4469,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4483,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4497,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4511,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4522,10 +4537,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4539,7 +4554,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4553,7 +4568,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4567,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4581,7 +4596,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4595,7 +4610,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4609,7 +4624,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4623,7 +4638,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4637,7 +4652,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4651,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4665,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4679,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4693,7 +4708,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4707,7 +4722,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4718,10 +4733,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4735,7 +4750,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4749,7 +4764,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4763,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4777,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4788,10 +4803,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4805,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>269</v>
+        <v>449</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4819,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>295</v>
+        <v>450</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4861,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4875,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4889,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>411</v>
+        <v>455</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4903,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>456</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4917,7 +4932,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4928,10 +4943,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4942,10 +4957,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4959,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4973,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4984,10 +4999,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5001,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5015,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5029,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5043,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5057,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5071,7 +5086,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5082,10 +5097,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5099,7 +5114,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5113,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5127,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5155,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5169,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5183,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5197,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5211,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>295</v>
+        <v>475</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5225,7 +5240,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5239,7 +5254,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5253,7 +5268,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5267,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5281,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5295,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5309,7 +5324,7 @@
         <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5323,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5334,10 +5349,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5351,7 +5366,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5365,7 +5380,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5379,7 +5394,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>392</v>
+        <v>487</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5393,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5407,7 +5422,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
